--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-06)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-223</v>
+        <v>-224</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-220</v>
+        <v>-221</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-220</v>
+        <v>-221</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-202</v>
+        <v>-203</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-201</v>
+        <v>-202</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-196</v>
+        <v>-197</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-196</v>
+        <v>-197</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-191</v>
+        <v>-192</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-190</v>
+        <v>-191</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-181</v>
+        <v>-182</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-181</v>
+        <v>-182</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-179</v>
+        <v>-180</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-162</v>
+        <v>-163</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-154</v>
+        <v>-155</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-133</v>
+        <v>-134</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-07)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-08)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-224</v>
+        <v>-225</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-221</v>
+        <v>-222</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-221</v>
+        <v>-222</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-202</v>
+        <v>-203</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-197</v>
+        <v>-198</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-197</v>
+        <v>-198</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-195</v>
+        <v>-196</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-191</v>
+        <v>-192</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-182</v>
+        <v>-183</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-182</v>
+        <v>-183</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-180</v>
+        <v>-181</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-166</v>
+        <v>-167</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-160</v>
+        <v>-161</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-157</v>
+        <v>-158</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-157</v>
+        <v>-158</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-140</v>
+        <v>-141</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-140</v>
+        <v>-141</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-137</v>
+        <v>-138</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-137</v>
+        <v>-138</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-134</v>
+        <v>-135</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-130</v>
+        <v>-131</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-130</v>
+        <v>-131</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-08)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-09)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-225</v>
+        <v>-226</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-222</v>
+        <v>-223</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-222</v>
+        <v>-223</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-198</v>
+        <v>-199</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-198</v>
+        <v>-199</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-196</v>
+        <v>-197</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-181</v>
+        <v>-182</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-167</v>
+        <v>-168</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-161</v>
+        <v>-162</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-158</v>
+        <v>-159</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-158</v>
+        <v>-159</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-145</v>
+        <v>-146</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-141</v>
+        <v>-142</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-141</v>
+        <v>-142</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-138</v>
+        <v>-139</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-138</v>
+        <v>-139</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-135</v>
+        <v>-136</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-09)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-231</v>
+        <v>-232</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-226</v>
+        <v>-227</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-223</v>
+        <v>-224</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-223</v>
+        <v>-224</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-197</v>
+        <v>-198</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-195</v>
+        <v>-196</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-182</v>
+        <v>-183</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-166</v>
+        <v>-167</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-162</v>
+        <v>-163</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-157</v>
+        <v>-158</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-154</v>
+        <v>-155</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-10)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-232</v>
+        <v>-246</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-227</v>
+        <v>-241</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-224</v>
+        <v>-238</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-224</v>
+        <v>-238</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-220</v>
+        <v>-234</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-220</v>
+        <v>-234</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-219</v>
+        <v>-233</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-219</v>
+        <v>-233</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-206</v>
+        <v>-220</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-205</v>
+        <v>-219</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-200</v>
+        <v>-214</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-200</v>
+        <v>-214</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-198</v>
+        <v>-212</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-196</v>
+        <v>-210</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-195</v>
+        <v>-209</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-194</v>
+        <v>-208</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-189</v>
+        <v>-203</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-189</v>
+        <v>-203</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-189</v>
+        <v>-203</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-189</v>
+        <v>-203</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-189</v>
+        <v>-203</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-189</v>
+        <v>-203</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-188</v>
+        <v>-202</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-187</v>
+        <v>-201</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-187</v>
+        <v>-201</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-185</v>
+        <v>-199</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-185</v>
+        <v>-199</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-183</v>
+        <v>-197</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-178</v>
+        <v>-192</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-178</v>
+        <v>-192</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-178</v>
+        <v>-192</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-178</v>
+        <v>-192</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-175</v>
+        <v>-189</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-175</v>
+        <v>-189</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-174</v>
+        <v>-188</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-173</v>
+        <v>-187</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-173</v>
+        <v>-187</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-173</v>
+        <v>-187</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-172</v>
+        <v>-186</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-172</v>
+        <v>-186</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-169</v>
+        <v>-183</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-167</v>
+        <v>-181</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-166</v>
+        <v>-180</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-163</v>
+        <v>-177</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-160</v>
+        <v>-174</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-160</v>
+        <v>-174</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-158</v>
+        <v>-172</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-155</v>
+        <v>-169</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-154</v>
+        <v>-168</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-154</v>
+        <v>-168</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-152</v>
+        <v>-166</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-150</v>
+        <v>-164</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-150</v>
+        <v>-164</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-147</v>
+        <v>-161</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-143</v>
+        <v>-157</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-143</v>
+        <v>-157</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-140</v>
+        <v>-154</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-140</v>
+        <v>-154</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-137</v>
+        <v>-151</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-133</v>
+        <v>-147</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-133</v>
+        <v>-147</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-24)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-246</v>
+        <v>-247</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-241</v>
+        <v>-242</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-238</v>
+        <v>-239</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-238</v>
+        <v>-239</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-233</v>
+        <v>-234</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-233</v>
+        <v>-234</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-220</v>
+        <v>-221</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-210</v>
+        <v>-211</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-209</v>
+        <v>-210</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-208</v>
+        <v>-209</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-202</v>
+        <v>-203</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-201</v>
+        <v>-202</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-201</v>
+        <v>-202</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-197</v>
+        <v>-198</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-181</v>
+        <v>-182</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-180</v>
+        <v>-181</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-166</v>
+        <v>-167</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-161</v>
+        <v>-162</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-157</v>
+        <v>-158</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-157</v>
+        <v>-158</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-154</v>
+        <v>-155</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-154</v>
+        <v>-155</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-25)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-247</v>
+        <v>-248</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-242</v>
+        <v>-243</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-239</v>
+        <v>-240</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-239</v>
+        <v>-240</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-221</v>
+        <v>-222</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-220</v>
+        <v>-221</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-211</v>
+        <v>-212</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-210</v>
+        <v>-211</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-209</v>
+        <v>-210</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-202</v>
+        <v>-203</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-202</v>
+        <v>-203</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-200</v>
+        <v>-201</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-200</v>
+        <v>-201</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-198</v>
+        <v>-199</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-190</v>
+        <v>-191</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-190</v>
+        <v>-191</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-182</v>
+        <v>-183</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-181</v>
+        <v>-182</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-178</v>
+        <v>-179</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-167</v>
+        <v>-168</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-162</v>
+        <v>-163</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-158</v>
+        <v>-159</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-158</v>
+        <v>-159</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-26)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-248</v>
+        <v>-249</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-243</v>
+        <v>-244</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-240</v>
+        <v>-241</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-240</v>
+        <v>-241</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-236</v>
+        <v>-237</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-236</v>
+        <v>-237</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-222</v>
+        <v>-223</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-221</v>
+        <v>-222</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-211</v>
+        <v>-212</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-210</v>
+        <v>-211</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-201</v>
+        <v>-202</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-201</v>
+        <v>-202</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-191</v>
+        <v>-192</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-191</v>
+        <v>-192</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-190</v>
+        <v>-191</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-182</v>
+        <v>-183</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-179</v>
+        <v>-180</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-166</v>
+        <v>-167</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-166</v>
+        <v>-167</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-09-27)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-249</v>
+        <v>-253</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-244</v>
+        <v>-248</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-241</v>
+        <v>-245</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-241</v>
+        <v>-245</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-237</v>
+        <v>-241</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-237</v>
+        <v>-241</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-236</v>
+        <v>-240</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-236</v>
+        <v>-240</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-223</v>
+        <v>-227</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-222</v>
+        <v>-226</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-217</v>
+        <v>-221</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-217</v>
+        <v>-221</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-215</v>
+        <v>-219</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-213</v>
+        <v>-217</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-212</v>
+        <v>-216</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-211</v>
+        <v>-215</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-205</v>
+        <v>-209</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-204</v>
+        <v>-208</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-204</v>
+        <v>-208</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-202</v>
+        <v>-206</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-202</v>
+        <v>-206</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-200</v>
+        <v>-204</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-195</v>
+        <v>-199</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-195</v>
+        <v>-199</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-195</v>
+        <v>-199</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-195</v>
+        <v>-199</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-192</v>
+        <v>-196</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-192</v>
+        <v>-196</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-191</v>
+        <v>-195</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-190</v>
+        <v>-194</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-190</v>
+        <v>-194</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-190</v>
+        <v>-194</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-189</v>
+        <v>-193</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-189</v>
+        <v>-193</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-186</v>
+        <v>-190</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-184</v>
+        <v>-188</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-183</v>
+        <v>-187</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-180</v>
+        <v>-184</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-177</v>
+        <v>-181</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-177</v>
+        <v>-181</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-175</v>
+        <v>-179</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-172</v>
+        <v>-176</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-171</v>
+        <v>-175</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-171</v>
+        <v>-175</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-169</v>
+        <v>-173</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-167</v>
+        <v>-171</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-167</v>
+        <v>-171</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-164</v>
+        <v>-168</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-160</v>
+        <v>-164</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-160</v>
+        <v>-164</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-157</v>
+        <v>-161</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-157</v>
+        <v>-161</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-154</v>
+        <v>-158</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-150</v>
+        <v>-154</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-150</v>
+        <v>-154</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-10-01)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-253</v>
+        <v>-265</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-248</v>
+        <v>-260</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-245</v>
+        <v>-257</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-245</v>
+        <v>-257</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-241</v>
+        <v>-253</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-241</v>
+        <v>-253</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-240</v>
+        <v>-252</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-240</v>
+        <v>-252</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-227</v>
+        <v>-239</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-226</v>
+        <v>-238</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-221</v>
+        <v>-233</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-221</v>
+        <v>-233</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-219</v>
+        <v>-231</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-217</v>
+        <v>-229</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-216</v>
+        <v>-228</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-215</v>
+        <v>-227</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-210</v>
+        <v>-222</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-210</v>
+        <v>-222</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-210</v>
+        <v>-222</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-210</v>
+        <v>-222</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-210</v>
+        <v>-222</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-210</v>
+        <v>-222</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-209</v>
+        <v>-221</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-208</v>
+        <v>-220</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-208</v>
+        <v>-220</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-206</v>
+        <v>-218</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-206</v>
+        <v>-218</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-204</v>
+        <v>-216</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-199</v>
+        <v>-211</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-199</v>
+        <v>-211</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-199</v>
+        <v>-211</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-199</v>
+        <v>-211</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-196</v>
+        <v>-208</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-196</v>
+        <v>-208</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-195</v>
+        <v>-207</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-194</v>
+        <v>-206</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-194</v>
+        <v>-206</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-194</v>
+        <v>-206</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-193</v>
+        <v>-205</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-193</v>
+        <v>-205</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-190</v>
+        <v>-202</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-188</v>
+        <v>-200</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-187</v>
+        <v>-199</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-184</v>
+        <v>-196</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-181</v>
+        <v>-193</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-181</v>
+        <v>-193</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-179</v>
+        <v>-191</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-176</v>
+        <v>-188</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-175</v>
+        <v>-187</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-175</v>
+        <v>-187</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-173</v>
+        <v>-185</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-171</v>
+        <v>-183</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-171</v>
+        <v>-183</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-168</v>
+        <v>-180</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-164</v>
+        <v>-176</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-164</v>
+        <v>-176</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-161</v>
+        <v>-173</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-161</v>
+        <v>-173</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-158</v>
+        <v>-170</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-154</v>
+        <v>-166</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-154</v>
+        <v>-166</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-10-13)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-265</v>
+        <v>-269</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-260</v>
+        <v>-264</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-257</v>
+        <v>-261</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-257</v>
+        <v>-261</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-253</v>
+        <v>-257</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-253</v>
+        <v>-257</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-252</v>
+        <v>-256</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-252</v>
+        <v>-256</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-239</v>
+        <v>-243</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-238</v>
+        <v>-242</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-233</v>
+        <v>-237</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-233</v>
+        <v>-237</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-231</v>
+        <v>-235</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-229</v>
+        <v>-233</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-228</v>
+        <v>-232</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-227</v>
+        <v>-231</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-222</v>
+        <v>-226</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-222</v>
+        <v>-226</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-222</v>
+        <v>-226</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-222</v>
+        <v>-226</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-222</v>
+        <v>-226</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-222</v>
+        <v>-226</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-221</v>
+        <v>-225</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-220</v>
+        <v>-224</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-220</v>
+        <v>-224</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-218</v>
+        <v>-222</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-218</v>
+        <v>-222</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-216</v>
+        <v>-220</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-211</v>
+        <v>-215</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-211</v>
+        <v>-215</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-211</v>
+        <v>-215</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-211</v>
+        <v>-215</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-208</v>
+        <v>-212</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-208</v>
+        <v>-212</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-207</v>
+        <v>-211</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-206</v>
+        <v>-210</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-205</v>
+        <v>-209</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-205</v>
+        <v>-209</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-202</v>
+        <v>-206</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-200</v>
+        <v>-204</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-199</v>
+        <v>-203</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-196</v>
+        <v>-200</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-193</v>
+        <v>-197</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-193</v>
+        <v>-197</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-191</v>
+        <v>-195</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-188</v>
+        <v>-192</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-187</v>
+        <v>-191</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-187</v>
+        <v>-191</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-185</v>
+        <v>-189</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-183</v>
+        <v>-187</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-183</v>
+        <v>-187</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-180</v>
+        <v>-184</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-176</v>
+        <v>-180</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-176</v>
+        <v>-180</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-173</v>
+        <v>-177</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-173</v>
+        <v>-177</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-170</v>
+        <v>-174</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-166</v>
+        <v>-170</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-166</v>
+        <v>-170</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-10-17)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-269</v>
+        <v>-271</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-264</v>
+        <v>-266</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-261</v>
+        <v>-263</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-261</v>
+        <v>-263</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-257</v>
+        <v>-259</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-257</v>
+        <v>-259</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-256</v>
+        <v>-258</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-256</v>
+        <v>-258</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-243</v>
+        <v>-245</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-242</v>
+        <v>-244</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-237</v>
+        <v>-239</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-237</v>
+        <v>-239</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-235</v>
+        <v>-237</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-233</v>
+        <v>-235</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-232</v>
+        <v>-234</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-231</v>
+        <v>-233</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-226</v>
+        <v>-228</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-226</v>
+        <v>-228</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-226</v>
+        <v>-228</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-226</v>
+        <v>-228</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-226</v>
+        <v>-228</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-226</v>
+        <v>-228</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-225</v>
+        <v>-227</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-224</v>
+        <v>-226</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-224</v>
+        <v>-226</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-222</v>
+        <v>-224</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-222</v>
+        <v>-224</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-220</v>
+        <v>-222</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-215</v>
+        <v>-217</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-215</v>
+        <v>-217</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-215</v>
+        <v>-217</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-215</v>
+        <v>-217</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-212</v>
+        <v>-214</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-212</v>
+        <v>-214</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-211</v>
+        <v>-213</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-210</v>
+        <v>-212</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-210</v>
+        <v>-212</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-210</v>
+        <v>-212</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-209</v>
+        <v>-211</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-209</v>
+        <v>-211</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-206</v>
+        <v>-208</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-204</v>
+        <v>-206</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-203</v>
+        <v>-205</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-200</v>
+        <v>-202</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-197</v>
+        <v>-199</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-197</v>
+        <v>-199</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-195</v>
+        <v>-197</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-192</v>
+        <v>-194</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-191</v>
+        <v>-193</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-191</v>
+        <v>-193</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-189</v>
+        <v>-191</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-187</v>
+        <v>-189</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-187</v>
+        <v>-189</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-184</v>
+        <v>-186</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-180</v>
+        <v>-182</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-180</v>
+        <v>-182</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-177</v>
+        <v>-179</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-177</v>
+        <v>-179</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-174</v>
+        <v>-176</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-170</v>
+        <v>-172</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-170</v>
+        <v>-172</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-10-19)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-271</v>
+        <v>-272</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-266</v>
+        <v>-267</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-259</v>
+        <v>-260</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-259</v>
+        <v>-260</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-258</v>
+        <v>-259</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-258</v>
+        <v>-259</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-245</v>
+        <v>-246</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-244</v>
+        <v>-245</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-239</v>
+        <v>-240</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-239</v>
+        <v>-240</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-237</v>
+        <v>-238</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-233</v>
+        <v>-234</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-227</v>
+        <v>-228</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-226</v>
+        <v>-227</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-226</v>
+        <v>-227</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-224</v>
+        <v>-225</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-224</v>
+        <v>-225</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-222</v>
+        <v>-223</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-211</v>
+        <v>-212</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-211</v>
+        <v>-212</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-208</v>
+        <v>-209</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-206</v>
+        <v>-207</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-202</v>
+        <v>-203</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-197</v>
+        <v>-198</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-191</v>
+        <v>-192</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-182</v>
+        <v>-183</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-182</v>
+        <v>-183</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-179</v>
+        <v>-180</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-179</v>
+        <v>-180</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-10-20)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-272</v>
+        <v>-273</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-267</v>
+        <v>-268</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-264</v>
+        <v>-265</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-264</v>
+        <v>-265</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-260</v>
+        <v>-261</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-260</v>
+        <v>-261</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-259</v>
+        <v>-260</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-259</v>
+        <v>-260</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-246</v>
+        <v>-247</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-245</v>
+        <v>-246</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-240</v>
+        <v>-241</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-240</v>
+        <v>-241</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-238</v>
+        <v>-239</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-236</v>
+        <v>-237</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-227</v>
+        <v>-228</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-227</v>
+        <v>-228</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-225</v>
+        <v>-226</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-225</v>
+        <v>-226</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-223</v>
+        <v>-224</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-209</v>
+        <v>-210</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-207</v>
+        <v>-208</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-206</v>
+        <v>-207</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-200</v>
+        <v>-201</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-200</v>
+        <v>-201</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-198</v>
+        <v>-199</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-195</v>
+        <v>-196</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-192</v>
+        <v>-193</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-190</v>
+        <v>-191</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-190</v>
+        <v>-191</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-180</v>
+        <v>-181</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-180</v>
+        <v>-181</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>

--- a/supply/data/atlas_zakup.xlsx
+++ b/supply/data/atlas_zakup.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ATLAS · план закупа — заказать (срез 2026-10-21)</t>
+          <t>ATLAS · план закупа — заказать (срез 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-273</v>
+        <v>-274</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-268</v>
+        <v>-269</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-265</v>
+        <v>-266</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-265</v>
+        <v>-266</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-261</v>
+        <v>-262</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-261</v>
+        <v>-262</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-260</v>
+        <v>-261</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-260</v>
+        <v>-261</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-247</v>
+        <v>-248</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-246</v>
+        <v>-247</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-241</v>
+        <v>-242</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-241</v>
+        <v>-242</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-239</v>
+        <v>-240</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-237</v>
+        <v>-238</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-236</v>
+        <v>-237</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-230</v>
+        <v>-231</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-229</v>
+        <v>-230</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-228</v>
+        <v>-229</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-226</v>
+        <v>-227</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-226</v>
+        <v>-227</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-224</v>
+        <v>-225</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-210</v>
+        <v>-211</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-208</v>
+        <v>-209</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-207</v>
+        <v>-208</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-201</v>
+        <v>-202</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-201</v>
+        <v>-202</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-196</v>
+        <v>-197</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-195</v>
+        <v>-196</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-195</v>
+        <v>-196</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-191</v>
+        <v>-192</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-191</v>
+        <v>-192</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-188</v>
+        <v>-189</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-184</v>
+        <v>-185</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-181</v>
+        <v>-182</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-181</v>
+        <v>-182</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-178</v>
+        <v>-179</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
